--- a/artfynd/A 12894-2022 artfynd.xlsx
+++ b/artfynd/A 12894-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>113380414</v>
       </c>
       <c r="B3" t="n">
-        <v>56271</v>
+        <v>56272</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 12894-2022 artfynd.xlsx
+++ b/artfynd/A 12894-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>113380414</v>
       </c>
       <c r="B3" t="n">
-        <v>56272</v>
+        <v>56275</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 12894-2022 artfynd.xlsx
+++ b/artfynd/A 12894-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>113380414</v>
       </c>
       <c r="B3" t="n">
-        <v>56275</v>
+        <v>56279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 12894-2022 artfynd.xlsx
+++ b/artfynd/A 12894-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>113380414</v>
       </c>
       <c r="B3" t="n">
-        <v>56279</v>
+        <v>56286</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 12894-2022 artfynd.xlsx
+++ b/artfynd/A 12894-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>113380414</v>
       </c>
       <c r="B3" t="n">
-        <v>56286</v>
+        <v>56288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 12894-2022 artfynd.xlsx
+++ b/artfynd/A 12894-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>113380414</v>
       </c>
       <c r="B3" t="n">
-        <v>56288</v>
+        <v>56316</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 12894-2022 artfynd.xlsx
+++ b/artfynd/A 12894-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
